--- a/stories/arbres/ATOM-REL.AMI.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est dans le jardin. Papa arrose les fleurs. Sara a des cerceaux. Les cerceaux sont verts. Zoé est là aussi. Sara veut jouer. Papa dit : tu peux inviter. Inviter, c'est demander. Sara dit : tu veux jouer ? Zoé secoue la tête. Zoé dit : non. Sara a le ventre serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Sara dit : d'accord. Elle joue avec papa. Les cerceaux roulent. Zoé joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sara n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Sara sourit un peu. Papa reste près d'elle.</t>
+          <t>Sara est dans le jardin. Papa arrose les fleurs. Sara a des cerceaux. Les cerceaux sont verts. Zoé est là aussi. Sara veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Zoé secoue la tête. Non. Sara a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les cerceaux roulent. Zoé joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sara n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non. Sara sourit un peu. Papa reste près d'elle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,21 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara est dans le jardin. Papa arrose les fleurs. Sara a des cerceaux. Les cerceaux sont verts. Zoé est là aussi. Sara veut jouer.
+papa|Tu peux inviter. Inviter, c'est demander.
+enfant-f|Tu veux jouer ?
+narrateur|Zoé secoue la tête.
+copine|Non.
+narrateur|Sara a le ventre serré. Papa s'approche.
+papa|On peut accepter un non. Accepter un non, c'est possible.
+enfant-f|D'accord. Elle joue avec papa.
+narrateur|Les cerceaux roulent. Zoé joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sara n'insiste pas.
+papa|Merci. Tu as su inviter. Tu as su accepter un non.
+narrateur|Sara sourit un peu. Papa reste près d'elle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé dit non. Que fait Sara ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a su inviter. Zoé a dit non. Sara a pu accepter un non. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1832,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara range un cerceau. Papa ferme le robinet.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1999,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1320,6 +1325,7 @@
 narrateur|Sara sourit un peu. Papa reste près d'elle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Zoé dit non. Que fait Sara ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Sara a su inviter. Zoé a dit non. Sara a pu accepter un non. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Sara range un cerceau. Papa ferme le robinet.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sara invite Zoé à jouer</t>
+          <t>Les cerceaux de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Des cerceaux verts attendent dans l'herbe. Sarah invite Nina. Nina dit non. Sarah joue avec papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara est dans le jardin. Papa arrose les fleurs. Sara a des cerceaux. Les cerceaux sont verts. Zoé est là aussi. Sara veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Zoé secoue la tête. Non. Sara a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les cerceaux roulent. Zoé joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sara n'insiste pas. Merci. Tu as su inviter. Tu as su accepter un non. Sara sourit un peu. Papa reste près d'elle.</t>
+          <t>Le tuyau est enroulé. Il brille un peu. Des pétales sont mouillés. Ils collent à l'herbe. Des cerceaux verts attendent. Papa arrose les fleurs. L'eau fait un petit bruit. Sarah, viens. En ce moment, Sarah prend un cerceau. Le plastique est lisse et frais. Il est vert, papa. Oui. Nina est là aussi. Nina a un seau. Sarah veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Nina secoue la tête. Sarah a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les cerceaux roulent. Nina joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sarah continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Sarah sourit un peu. Tu as fait du bon travail. Le jeu reste doux. Le cerceau roule. Oui. Sarah pousse encore le cerceau. Il s'arrête près d'une fleur. Il est vert. Oui. Tu as invité. Nina a dit non. Tu as accepté un non. D'accord. Le seau de Nina fait un petit bruit. L'eau brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara est dans le jardin. Papa arrose les fleurs. Sara a des cerceaux. Les cerceaux sont verts. Zoé est là aussi. Sara veut jouer.
-papa|Tu peux inviter. Inviter, c'est demander.
+          <t>narrateur|Le tuyau est enroulé.
+narrateur|Il brille un peu.
+narrateur|Des pétales sont mouillés.
+narrateur|Ils collent à l'herbe.
+narrateur|Des cerceaux verts attendent.
+narrateur|Papa arrose les fleurs.
+narrateur|L'eau fait un petit bruit.
+papa|Sarah, viens.
+narrateur|En ce moment, Sarah prend un cerceau.
+narrateur|Le plastique est lisse et frais.
+enfant-f|Il est vert, papa.
+papa|Oui.
+narrateur|Nina est là aussi.
+narrateur|Nina a un seau.
+narrateur|Sarah veut jouer.
+papa|Tu peux inviter.
+papa|Inviter, c'est demander.
 enfant-f|Tu veux jouer ?
-narrateur|Zoé secoue la tête.
 copine|Non.
-narrateur|Sara a le ventre serré. Papa s'approche.
-papa|On peut accepter un non. Accepter un non, c'est possible.
-enfant-f|D'accord. Elle joue avec papa.
-narrateur|Les cerceaux roulent. Zoé joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sara n'insiste pas.
-papa|Merci. Tu as su inviter. Tu as su accepter un non.
-narrateur|Sara sourit un peu. Papa reste près d'elle.</t>
+narrateur|Nina secoue la tête.
+narrateur|Sarah a le ventre serré.
+narrateur|Papa s'approche.
+papa|On peut accepter un non.
+papa|Accepter un non, c'est possible.
+enfant-f|D'accord.
+narrateur|Elle joue avec papa.
+narrateur|Les cerceaux roulent.
+narrateur|Nina joue avec un seau.
+narrateur|L'eau brille au soleil.
+narrateur|Une abeille passe.
+narrateur|Les fleurs sentent bon.
+narrateur|Sarah continue son jeu.
+papa|Merci.
+papa|Tu as su inviter.
+papa|Tu as su accepter un non.
+narrateur|Sarah sourit un peu.
+papa|Tu as fait du bon travail.
+papa|Le jeu reste doux.
+enfant-f|Le cerceau roule.
+papa|Oui.
+narrateur|Sarah pousse encore le cerceau.
+narrateur|Il s'arrête près d'une fleur.
+enfant-f|Il est vert.
+papa|Oui.
+papa|Tu as invité.
+papa|Nina a dit non.
+papa|Tu as accepté un non.
+enfant-f|D'accord.
+narrateur|Le seau de Nina fait un petit bruit.
+narrateur|L'eau brille encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1350,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Zoé dit non. Que fait Sara ?</t>
+          <t>Nina dit non. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1557,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Zoé dit non. Que fait Sara ?</t>
+          <t>narrateur|Nina dit non.
+narrateur|Que fait Sarah ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1586,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a su inviter. Zoé a dit non. Sara a pu accepter un non. Papa est là.</t>
+          <t>Sarah a su inviter. Nina a dit non. Sarah a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui. Bravo. Tu as fait du bon travail. Le cerceau s'arrête dans l'herbe. Nina verse de l'eau. Sarah reprend un cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Les pétales restent mouillés. Ils collent. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une abeille passe encore. Sarah attend son tour avec papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1730,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a su inviter. Zoé a dit non. Sara a pu accepter un non. Papa est là.</t>
+          <t>narrateur|Sarah a su inviter.
+narrateur|Nina a dit non.
+narrateur|Sarah a pu accepter un non.
+papa|Je suis près de toi.
+papa|Tu as accepté un non ?
+enfant-f|Oui.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le cerceau s'arrête dans l'herbe.
+narrateur|Nina verse de l'eau.
+narrateur|Sarah reprend un cerceau.
+enfant-f|À toi, papa.
+papa|Merci.
+papa|On peut inviter.
+papa|On peut accepter un non.
+narrateur|Les pétales restent mouillés.
+enfant-f|Ils collent.
+papa|Oui.
+papa|Tu as demandé.
+papa|Tu as accepté un non.
+enfant-f|Oui, papa.
+narrateur|Une abeille passe encore.
+narrateur|Sarah attend son tour avec papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sara range un cerceau. Papa ferme le robinet.</t>
+          <t>On range un cerceau ? Oui. Sarah range un cerceau. Papa ferme le robinet. Le tuyau reste enroulé. Tu as fini de jouer ? Oui, papa. Merci. Bravo. Nina agite la main. Au revoir. Au revoir. Les fleurs sentent encore. Tu as su inviter, Sarah. Oui. L'herbe est un peu mouillée. Les cerceaux verts attendent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1916,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sara range un cerceau. Papa ferme le robinet.</t>
+          <t>papa|On range un cerceau ?
+enfant-f|Oui.
+narrateur|Sarah range un cerceau.
+narrateur|Papa ferme le robinet.
+narrateur|Le tuyau reste enroulé.
+papa|Tu as fini de jouer ?
+enfant-f|Oui, papa.
+papa|Merci.
+papa|Bravo.
+narrateur|Nina agite la main.
+copine|Au revoir.
+enfant-f|Au revoir.
+narrateur|Les fleurs sentent encore.
+papa|Tu as su inviter, Sarah.
+enfant-f|Oui.
+narrateur|L'herbe est un peu mouillée.
+narrateur|Les cerceaux verts attendent.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai invité. Nina a dit non. Tu as accepté un non. Bravo, Sarah. L'herbe redevient calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2100,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai invité.
+enfant-f|Nina a dit non.
+papa|Tu as accepté un non.
+papa|Bravo, Sarah.
+narrateur|L'herbe redevient calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le tuyau est enroulé. Il brille un peu. Des pétales sont mouillés. Ils collent à l'herbe. Des cerceaux verts attendent. Papa arrose les fleurs. L'eau fait un petit bruit. Sarah, viens. En ce moment, Sarah prend un cerceau. Le plastique est lisse et frais. Il est vert, papa. Oui. Nina est là aussi. Nina a un seau. Sarah veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Nina secoue la tête. Sarah a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les cerceaux roulent. Nina joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sarah continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Sarah sourit un peu. Tu as fait du bon travail. Le jeu reste doux. Le cerceau roule. Oui. Sarah pousse encore le cerceau. Il s'arrête près d'une fleur. Il est vert. Oui. Tu as invité. Nina a dit non. Tu as accepté un non. D'accord. Le seau de Nina fait un petit bruit. L'eau brille encore.</t>
+          <t>Le tuyau est enroulé. Il brille un peu. Des pétales sont mouillés. Ils collent à l'herbe. Des cerceaux verts attendent. Papa arrose les fleurs. L'eau fait un petit bruit. Sarah, viens. En ce moment, Sarah prend un cerceau. Le plastique est lisse et frais. Il est vert, papa. Oui. Nina est là aussi. Nina a un seau. Sarah veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Nina secoue la tête. Sarah a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les cerceaux roulent. Nina joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sarah continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Sarah sourit un peu. Le jeu reste doux. Le cerceau roule. Oui. Sarah pousse encore le cerceau. Il s'arrête près d'une fleur. Il est vert. Oui. Tu as invité. Nina a dit non. Tu as accepté un non. D'accord. Le seau de Nina fait un petit bruit. L'eau brille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara est dans le jardin. Papa arrose les fleurs. Sara a des cerceaux. Les cerceaux sont verts. Zoé est là aussi. Sara veut jouer. Papa dit : tu peux &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Inviter, c'est demander. Sara dit : tu veux jouer ? Zoé secoue la tête. Zoé dit : non. Sara a le ventre serré. Papa s'approche. Papa dit : on peut accepter un non. Accepter un non, c'est possible. Sara dit : d'accord. Elle joue avec papa. Les cerceaux roulent. Zoé joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sara n'insiste pas. Papa dit : merci. Tu as su inviter. Tu as su accepter un non. Sara sourit un peu. Papa reste près d'elle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le tuyau est enroulé. Il brille un peu. Des pétales sont mouillés. Ils collent à l'herbe. Des cerceaux verts attendent. Papa arrose les fleurs. L'eau fait un petit bruit. Sarah, viens. En ce moment, Sarah prend un cerceau. Le plastique est lisse et frais. Il est vert, papa. Oui. Nina est là aussi. Nina a un seau. Sarah veut jouer. Tu peux inviter. Inviter, c'est demander. Tu veux jouer ? Non. Nina secoue la tête. Sarah a le ventre serré. Papa s'approche. On peut accepter un non. Accepter un non, c'est possible. D'accord. Elle joue avec papa. Les cerceaux roulent. Nina joue avec un seau. L'eau brille au soleil. Une abeille passe. Les fleurs sentent bon. Sarah continue son jeu. Merci. Tu as su inviter. Tu as su accepter un non. Sarah sourit un peu. Le jeu reste doux. Le cerceau roule. Oui. Sarah pousse encore le cerceau. Il s'arrête près d'une fleur. Il est vert. Oui. Tu as invité. Nina a dit non. Tu as accepté un non. D'accord. Le seau de Nina fait un petit bruit. L'eau brille encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1360,7 +1360,6 @@
 papa|Tu as su inviter.
 papa|Tu as su accepter un non.
 narrateur|Sarah sourit un peu.
-papa|Tu as fait du bon travail.
 papa|Le jeu reste doux.
 enfant-f|Le cerceau roule.
 papa|Oui.
@@ -1376,7 +1375,6 @@
 narrateur|L'eau brille encore.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1406,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Zoé dit non. Que fait Sara ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina dit non. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1561,7 +1559,6 @@
 narrateur|Que fait Sarah ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1586,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a su inviter. Nina a dit non. Sarah a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui. Bravo. Tu as fait du bon travail. Le cerceau s'arrête dans l'herbe. Nina verse de l'eau. Sarah reprend un cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Les pétales restent mouillés. Ils collent. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une abeille passe encore. Sarah attend son tour avec papa.</t>
+          <t>Sarah a su inviter. Nina a dit non. Sarah a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui. Bravo. Le cerceau s'arrête dans l'herbe. Nina verse de l'eau. Sarah reprend un cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Les pétales restent mouillés. Ils collent. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une abeille passe encore. Sarah attend son tour avec papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Zoé a dit non. Sara a pu accepter un non. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a su inviter. Nina a dit non. Sarah a pu accepter un non. Je suis près de toi. Tu as accepté un non ? Oui. Bravo. Le cerceau s'arrête dans l'herbe. Nina verse de l'eau. Sarah reprend un cerceau. À toi, papa. Merci. On peut inviter. On peut accepter un non. Les pétales restent mouillés. Ils collent. Oui. Tu as demandé. Tu as accepté un non. Oui, papa. Une abeille passe encore. Sarah attend son tour avec papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1737,7 +1734,6 @@
 papa|Tu as accepté un non ?
 enfant-f|Oui.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 narrateur|Le cerceau s'arrête dans l'herbe.
 narrateur|Nina verse de l'eau.
 narrateur|Sarah reprend un cerceau.
@@ -1755,7 +1751,6 @@
 narrateur|Sarah attend son tour avec papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sara range un cerceau. Papa ferme le robinet.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range un cerceau ? Oui. Sarah range un cerceau. Papa ferme le robinet. Le tuyau reste enroulé. Tu as fini de jouer ? Oui, papa. Merci. Bravo. Nina agite la main. Au revoir. Au revoir. Les fleurs sentent encore. Tu as su inviter, Sarah. Oui. L'herbe est un peu mouillée. Les cerceaux verts attendent.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1935,7 +1930,6 @@
 narrateur|Les cerceaux verts attendent.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1960,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai invité. Nina a dit non. Tu as accepté un non. Bravo, Sarah. L'herbe redevient calme. L'histoire est finie.</t>
+          <t>J'ai invité. Nina a dit non. Tu as accepté un non. Bravo, Sarah. L'herbe redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai invité. Nina a dit non. Tu as accepté un non. Bravo, Sarah. L'herbe redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,11 +2098,9 @@
 enfant-f|Nina a dit non.
 papa|Tu as accepté un non.
 papa|Bravo, Sarah.
-narrateur|L'herbe redevient calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'herbe redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-01.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, Zoé, papa</t>
+          <t>Sarah, Nina, papa</t>
         </is>
       </c>
     </row>
